--- a/ScadaEngine.Engine/Modbus/Modbus範本.xlsx
+++ b/ScadaEngine.Engine/Modbus/Modbus範本.xlsx
@@ -29,6 +29,9 @@
   </x:si>
   <x:si>
     <x:t>ConnectTimeout</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DeviceName</x:t>
   </x:si>
   <x:si>
     <x:t>名稱 Name</x:t>
@@ -548,7 +551,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I27"/>
+  <x:dimension ref="A1:J27"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="24.710625" style="0" customWidth="1"/>
@@ -560,7 +563,7 @@
     <x:col min="9" max="9" width="16.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:9">
+    <x:row r="1" spans="1:10">
       <x:c r="A1" s="2" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -583,159 +586,163 @@
       <x:c r="H1" s="0">
         <x:v>1000</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:9">
+      <x:c r="I1" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:10">
       <x:c r="A2" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G2" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H2" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="I2" s="3" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:9">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:10">
       <x:c r="I3" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:9">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:10">
       <x:c r="I4" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:9">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:10">
       <x:c r="I5" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:9">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:10">
       <x:c r="I6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:9">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:10">
       <x:c r="I7" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:9">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:10">
       <x:c r="I8" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:9">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:10">
       <x:c r="I9" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:9">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:10">
       <x:c r="I10" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:9">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:10">
       <x:c r="I11" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:9">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:10">
       <x:c r="I12" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:9">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:10">
       <x:c r="I13" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:9">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:10">
       <x:c r="I14" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:9">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:10">
       <x:c r="I15" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:9">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:10">
       <x:c r="I16" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:9">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:10">
       <x:c r="I17" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:9">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:10">
       <x:c r="I18" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:9">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:10">
       <x:c r="I19" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:9">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:10">
       <x:c r="I20" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:9">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:10">
       <x:c r="I21" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:9">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:10">
       <x:c r="I22" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:9">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:10">
       <x:c r="I23" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:9">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:10">
       <x:c r="I24" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:9">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:10">
       <x:c r="I25" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:9">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:10">
       <x:c r="I26" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:9">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:10">
       <x:c r="I27" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
